--- a/education_forms/038_water_treaty_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/038_water_treaty_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Water Treaty Knowledge Quiz</t>
+          <t>What is the name of the water treaty that you are familiar with?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>num_types</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>How many types of water treaties are there?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>main_goal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Brief description of the form</t>
-        </is>
-      </c>
+          <t>What is the main goal of a water treaty?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>main_responsible</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Who is the primary responsible for enforcing water treaties?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>main_benefits</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>What are the main benefits of having a water treaty?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Submitted By</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted At</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>submitted_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Submitted At</t>
+          <t>Submitted Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>submitted_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submitted Time</t>
+          <t>Submitted Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submitted_date</t>
+          <t>submitted_date_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submitted Date</t>
+          <t>Submitted Date-Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submitted_date_time</t>
+          <t>submitted_time_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Submitted Date-Time</t>
+          <t>Submitted Time 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submitted_date_time</t>
+          <t>form_description</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submitted Date-Time</t>
+          <t>Form Description</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submitted_date_time</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submitted Date-Time</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submitted_date_time</t>
+          <t>submitted_date_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submitted Date-Time</t>
+          <t>Submitted Date 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -846,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>submitted_time_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submitted Time</t>
+          <t>Submitted Time 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submitted Time</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>submitted_date_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submitted Time</t>
+          <t>Submitted Date 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>submitted_time_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Submitted Time</t>
+          <t>Submitted Time 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submitted Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Submitted Time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submitted Time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submitted Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submitted Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submitted Time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submitted Time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,100 +965,304 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>form_name_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>education_forms</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Education Forms</t>
+          <t>Agreement</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>form_name_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>treaty</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Treaty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>form_name_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>protocol</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Protocol</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>form_name_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>convention</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Convention</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>form_name_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>declaration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Declaration</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>form_name_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>accord</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Accord</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>form_name_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pact</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pact</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>form_name_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>agreement_on</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Agreement on</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>form_name_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>treaty_on</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Treaty on</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>form_name_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>protocol_on</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Protocol on</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>form_name_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>convention_on</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Convention on</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>main_responsible_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>united_nations</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>United Nations</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>main_responsible_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>main_responsible_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>international_community</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>International Community</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>main_responsible_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>global_community</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Global Community</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>main_responsible_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>national_government</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>National Government</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>submitted_by_choices</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>submitted_by_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
